--- a/astro-site/public/dl/restaurant-schedule-templates/07-employee-directory.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/07-employee-directory.xlsx
@@ -728,7 +728,7 @@
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>▸ Log each employee on one row of the "Staff Directory" tab. It holds 30, the same as the schedule (file 01 (Restaurant Schedule Template: Weekly &amp; Monthly Staff Rota)) and the review history (file 06 (Employee Performance Review Form)).</t>
+          <t>▸ Log each employee on one row of the "Staff Directory" tab. It holds 30, the same as the schedule (file 01 "Restaurant Schedule Template") and the review history (file 06 "Employee Performance Review Form").</t>
         </is>
       </c>
     </row>
@@ -1955,10 +1955,10 @@
     <mergeCell ref="A38:V38"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid employment type" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="kitgp-v2 · Invalid emp. type" prompt="Permanent, Temporary, Intern, Trainee or Seasonal." type="list" errorStyle="stop">
+    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid employment type" error="Pick a value from the list." promptTitle="Employment type" prompt="Permanent, Temporary, Intern, Trainee or Seasonal." type="list" errorStyle="stop">
       <formula1>"Permanent,Temporary,Intern,Trainee,Seasonal"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid full/part-time" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="kitgp-v2 · Invalid FT/PT" prompt="Full-time or Part-time. This is only a schedule label: under the FLSA, overtime depends on the hours worked in the workweek (over 40 h at 1.5×), not on the employment type." type="list" errorStyle="stop">
+    <dataValidation sqref="G5:G34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid full/part-time" error="Pick a value from the list." promptTitle="Full / part-time" prompt="Full-time or Part-time. This is only a schedule label: under the FLSA, overtime depends on the hours worked in the workweek (over 40 h at 1.5×), not on the employment type." type="list" errorStyle="stop">
       <formula1>"Full-time,Part-time"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3404,9 +3404,9 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Updates on open" prompt="This cell is =TODAY(). Excel recalculates it when the file opens. In a phone or Drive PREVIEW, which does not recalculate, you will see the date the kit was downloaded and that date's traffic lights: open it in Excel or LibreOffice before trusting the alerts."/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Red threshold" prompt="From here on the expiry is urgent. Thirty days is reasonable for a seasonal or temporary end date and more than enough to renew a food handler card or an alcohol server certificate."/>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Amber threshold" prompt="How far ahead you want to find out. Raise it if the training for a card or certificate is run by a third party and takes a while to give you a date."/>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Updates when opened" prompt="This cell is =TODAY(). Excel recalculates it when the file opens. A phone or Drive PREVIEW does not recalculate: you will see the download date and that date's traffic lights. Open it in Excel or LibreOffice before trusting the alerts."/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Red threshold (days)" prompt="From here on the expiry is urgent. Thirty days is reasonable for a seasonal or temporary end date and more than enough to renew a food handler card or an alcohol server certificate."/>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Amber threshold (days)" prompt="How far ahead you want to find out. Raise it if the training for a card or certificate is run by a third party and takes a while to give you a date."/>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
